--- a/downloads/Th2_pre_post+2h_results.xlsx
+++ b/downloads/Th2_pre_post+2h_results.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C4">
@@ -875,7 +875,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C7">
@@ -986,7 +986,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C10">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C13">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C16">

--- a/downloads/Th2_pre_post+2h_results.xlsx
+++ b/downloads/Th2_pre_post+2h_results.xlsx
@@ -624,7 +624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,6 +683,46 @@
           <t>pi_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eg_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eg_df</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>eg_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tf_k0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tf_side</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tf_g</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tf_lo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tf_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -720,6 +760,23 @@
       <c r="K2">
         <v>0.5519020502600689</v>
       </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>0.07488026499816079</v>
+      </c>
+      <c r="R2">
+        <v>-0.2618616778567599</v>
+      </c>
+      <c r="S2">
+        <v>0.4116222078530815</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -757,6 +814,23 @@
       <c r="K3">
         <v>0.6632033378850528</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>0.05654768198090474</v>
+      </c>
+      <c r="R3">
+        <v>-0.3717061431581836</v>
+      </c>
+      <c r="S3">
+        <v>0.4848015071199931</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -831,6 +905,23 @@
       <c r="K5">
         <v>0.5162925859836925</v>
       </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q5">
+        <v>0.07465809247046376</v>
+      </c>
+      <c r="R5">
+        <v>-0.2371030513014936</v>
+      </c>
+      <c r="S5">
+        <v>0.3864192362424211</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -868,6 +959,23 @@
       <c r="K6">
         <v>0.6178387837006332</v>
       </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>0.05618858539788446</v>
+      </c>
+      <c r="R6">
+        <v>-0.3402947300915262</v>
+      </c>
+      <c r="S6">
+        <v>0.4526719008872951</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -942,6 +1050,23 @@
       <c r="K8">
         <v>0.4775252513265287</v>
       </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q8">
+        <v>0.07437208233194006</v>
+      </c>
+      <c r="R8">
+        <v>-0.2102241050745071</v>
+      </c>
+      <c r="S8">
+        <v>0.3589682697383872</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -979,6 +1104,23 @@
       <c r="K9">
         <v>0.5684360580658627</v>
       </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q9">
+        <v>0.05572629769719783</v>
+      </c>
+      <c r="R9">
+        <v>-0.3062087043539795</v>
+      </c>
+      <c r="S9">
+        <v>0.4176612997483752</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1053,6 +1195,23 @@
       <c r="K11">
         <v>0.4345768239825573</v>
       </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q11">
+        <v>0.07398820881664349</v>
+      </c>
+      <c r="R11">
+        <v>-0.1805605656710179</v>
+      </c>
+      <c r="S11">
+        <v>0.3285369833043049</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1090,6 +1249,23 @@
       <c r="K12">
         <v>0.5136822396473445</v>
       </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q12">
+        <v>0.0551058833693969</v>
+      </c>
+      <c r="R12">
+        <v>-0.2686149569179733</v>
+      </c>
+      <c r="S12">
+        <v>0.3788267236567671</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1164,6 +1340,23 @@
       <c r="K14">
         <v>0.3857165955120968</v>
       </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q14">
+        <v>0.07344074632622601</v>
+      </c>
+      <c r="R14">
+        <v>-0.1470028044935429</v>
+      </c>
+      <c r="S14">
+        <v>0.2938842971459948</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1200,6 +1393,23 @@
       </c>
       <c r="K15">
         <v>0.4513535883247314</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q15">
+        <v>0.05422110893145671</v>
+      </c>
+      <c r="R15">
+        <v>-0.226124918888338</v>
+      </c>
+      <c r="S15">
+        <v>0.3345671367512514</v>
       </c>
     </row>
     <row r="16">
